--- a/data/trans_orig/P6716-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17450</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38599</t>
+          <t>38648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>27596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30849</t>
+          <t>30715</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>54129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13452</t>
+          <t>14043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31130</t>
+          <t>31125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56415</t>
+          <t>56395</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78495</t>
+          <t>78845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55628</t>
+          <t>55589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97811</t>
+          <t>98797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127048</t>
+          <t>129284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17488</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>20701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16529</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10537</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>27454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58415</t>
+          <t>56513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11872</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28965</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>24327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47734</t>
+          <t>48036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102200</t>
+          <t>100347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127555</t>
+          <t>126173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69557</t>
+          <t>68990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91486</t>
+          <t>91136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178166</t>
+          <t>177376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211307</t>
+          <t>210939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20152</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>36373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16209</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63505</t>
+          <t>62698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>50931</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21987</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67159</t>
+          <t>66507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54475</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>76555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49497</t>
+          <t>48352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92086</t>
+          <t>91296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>121788</t>
+          <t>120705</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,62 +2812,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5860</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>31519</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34435</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>34275</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>60195</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>56048</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26897</t>
+          <t>27554</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47574</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74759</t>
+          <t>76465</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62967</t>
+          <t>62461</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>87652</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44805</t>
+          <t>45799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65704</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115328</t>
+          <t>114478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>147623</t>
+          <t>146602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15486</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20747</t>
+          <t>20826</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25598</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40583</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21750</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>8408</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>37483</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>51268</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25695</t>
+          <t>26874</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>49116</t>
+          <t>49858</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73365</t>
+          <t>73296</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28061</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20795</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>40022</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40433</t>
+          <t>41896</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>35268</t>
+          <t>35459</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>59976</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>53376</t>
+          <t>53301</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>75337</t>
+          <t>76356</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>77485</t>
+          <t>77881</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>104671</t>
+          <t>106096</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,82 +4838,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>3065</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>8194</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>7863</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>3034</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>8254</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>7863</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>3709</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>14150</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27791</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>58035</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>89621</t>
+          <t>88848</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>34732</t>
+          <t>34862</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>58824</t>
+          <t>58622</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>100408</t>
+          <t>99410</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>139264</t>
+          <t>139313</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>46879</t>
+          <t>48045</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>75411</t>
+          <t>76325</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>38952</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>63948</t>
+          <t>64165</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>94104</t>
+          <t>93733</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>131906</t>
+          <t>128805</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>110104</t>
+          <t>109722</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>146735</t>
+          <t>143730</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>59151</t>
+          <t>58434</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>86983</t>
+          <t>85529</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>175639</t>
+          <t>176458</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>220844</t>
+          <t>221428</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>18313</t>
+          <t>16980</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>18063</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>42265</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>39831</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>68774</t>
+          <t>68365</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>37904</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>67370</t>
+          <t>65114</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>84838</t>
+          <t>85791</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>126388</t>
+          <t>123495</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>111746</t>
+          <t>115155</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>151075</t>
+          <t>154227</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>71598</t>
+          <t>70869</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>101431</t>
+          <t>100196</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>192709</t>
+          <t>193134</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>244101</t>
+          <t>243293</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>133232</t>
+          <t>134552</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>173822</t>
+          <t>173934</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>90227</t>
+          <t>90815</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>124298</t>
+          <t>124496</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>233137</t>
+          <t>237880</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>285405</t>
+          <t>287314</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>52219</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>87120</t>
+          <t>84912</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>77012</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>57676</t>
+          <t>58554</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>83702</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>125829</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>226886</t>
+          <t>228258</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>285938</t>
+          <t>288581</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>179451</t>
+          <t>177522</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>231325</t>
+          <t>231237</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>423210</t>
+          <t>422586</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>508088</t>
+          <t>496707</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>317329</t>
+          <t>320767</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>390213</t>
+          <t>384439</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>198333</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>253605</t>
+          <t>249894</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>532829</t>
+          <t>535456</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>621080</t>
+          <t>617638</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>671257</t>
+          <t>675599</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>753581</t>
+          <t>751415</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>413153</t>
+          <t>412159</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>475492</t>
+          <t>476624</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1111012</t>
+          <t>1112674</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1208422</t>
+          <t>1208325</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33096</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23098</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44666</t>
+          <t>44975</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>19430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37212</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75814</t>
+          <t>77180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>34841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26182</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43559</t>
+          <t>44719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68943</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34101</t>
+          <t>33135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>53838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84514</t>
+          <t>84698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116367</t>
+          <t>116001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>25818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46892</t>
+          <t>46875</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42251</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69623</t>
+          <t>69783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53023</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>27700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46047</t>
+          <t>45058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73469</t>
+          <t>72579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69231</t>
+          <t>70494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95704</t>
+          <t>95980</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54380</t>
+          <t>54886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76637</t>
+          <t>76304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>130483</t>
+          <t>132698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164390</t>
+          <t>165135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>16859</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33787</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34703</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57454</t>
+          <t>56122</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42190</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61695</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21022</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67122</t>
+          <t>66211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95090</t>
+          <t>93595</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35301</t>
+          <t>34582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56198</t>
+          <t>55986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,82 +8936,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>33894</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>25119</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>43895</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>40,19%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>29,79%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>79265</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>66408</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>93715</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>37,62%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>31,52%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>44,47%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>33894</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>25894</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>43303</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>40,19%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>30,7%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>51,35%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>79265</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>65343</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>92357</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>37,62%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>22738</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40176</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7704</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>17463</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60498</t>
+          <t>60595</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82209</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>57596</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105204</t>
+          <t>104162</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>132713</t>
+          <t>133178</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,63%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,62 +9868,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>5863</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,62 +9981,62 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>7206</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>5148</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17817</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>33197</t>
+          <t>32561</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45896</t>
+          <t>46126</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>21045</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36077</t>
+          <t>35525</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53490</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76925</t>
+          <t>77757</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>40006</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9715</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>35076</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57703</t>
+          <t>56993</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -10515,97 +10515,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4410</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>873</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>4630</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>6253</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>4140</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32676</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>32348</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>21631</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28133</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>50498</t>
+          <t>50654</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>50090</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>21328</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>37916</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>55506</t>
+          <t>56187</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>81939</t>
+          <t>82484</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>23841</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40390</t>
+          <t>40937</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>65581</t>
+          <t>65822</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>13027</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>32108</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36324</t>
+          <t>36358</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33633</t>
+          <t>33547</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>61215</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>29812</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>54155</t>
+          <t>54707</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22226</t>
+          <t>22867</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>57267</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>90108</t>
+          <t>92300</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>107224</t>
+          <t>106636</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>144284</t>
+          <t>144232</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>80765</t>
+          <t>80730</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>113537</t>
+          <t>113160</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>197116</t>
+          <t>195561</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>244706</t>
+          <t>247372</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>54403</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>86102</t>
+          <t>84503</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>47664</t>
+          <t>47458</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>74688</t>
+          <t>74299</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>108520</t>
+          <t>107818</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>149469</t>
+          <t>150760</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>86707</t>
+          <t>86129</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>122287</t>
+          <t>122964</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>58381</t>
+          <t>57147</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>87872</t>
+          <t>86618</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>153776</t>
+          <t>152532</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>199528</t>
+          <t>199093</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>22301</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>36284</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>63010</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>31982</t>
+          <t>32109</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>55202</t>
+          <t>56565</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>74964</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>110725</t>
+          <t>111491</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>102138</t>
+          <t>102080</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>136690</t>
+          <t>137113</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>65274</t>
+          <t>65007</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>94122</t>
+          <t>95491</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>176559</t>
+          <t>177715</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>222016</t>
+          <t>224582</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>136341</t>
+          <t>135860</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>172703</t>
+          <t>174078</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>92483</t>
+          <t>92021</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>238792</t>
+          <t>236971</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>286204</t>
+          <t>285131</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>35206</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>66203</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>78021</t>
+          <t>76274</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>119675</t>
+          <t>119216</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>66251</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>103824</t>
+          <t>103171</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>51937</t>
+          <t>51092</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>82652</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>126360</t>
+          <t>126075</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>174615</t>
+          <t>178353</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>285785</t>
+          <t>285020</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>351781</t>
+          <t>346451</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>216962</t>
+          <t>217748</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>274523</t>
+          <t>273258</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>521464</t>
+          <t>518717</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>604264</t>
+          <t>604195</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>361713</t>
+          <t>361422</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>432494</t>
+          <t>429420</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>245893</t>
+          <t>246588</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>301454</t>
+          <t>301393</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>621082</t>
+          <t>619278</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>711192</t>
+          <t>709876</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>538483</t>
+          <t>542482</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>617169</t>
+          <t>615831</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>377272</t>
+          <t>373985</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>438026</t>
+          <t>436224</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>935274</t>
+          <t>930975</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1032868</t>
+          <t>1034850</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6716-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18573</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17897</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38648</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14620</t>
+          <t>14524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31974</t>
+          <t>32731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27596</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30715</t>
+          <t>30234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54129</t>
+          <t>54827</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4159</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31125</t>
+          <t>31051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56395</t>
+          <t>57747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78845</t>
+          <t>79710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>55933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98797</t>
+          <t>96585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129284</t>
+          <t>128757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20701</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>37184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31493</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56513</t>
+          <t>58284</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28882</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24412</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48036</t>
+          <t>47936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100347</t>
+          <t>101806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126173</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68990</t>
+          <t>69427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91136</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177376</t>
+          <t>175927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>210939</t>
+          <t>211388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7702</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18244</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>35875</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33552</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62698</t>
+          <t>64896</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>51575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42228</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66507</t>
+          <t>67364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>54416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>76555</t>
+          <t>78078</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30976</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48352</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91296</t>
+          <t>90783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120705</t>
+          <t>120050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31519</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17010</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>35127</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34275</t>
+          <t>34785</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60195</t>
+          <t>58619</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56048</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49196</t>
+          <t>48945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>77273</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62461</t>
+          <t>63631</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88282</t>
+          <t>88971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45799</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66000</t>
+          <t>64547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114478</t>
+          <t>115065</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>146602</t>
+          <t>147014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11655</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>15459</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>41859</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,34%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>37483</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51268</t>
+          <t>51542</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>49858</t>
+          <t>48716</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>73296</t>
+          <t>72999</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28186</t>
+          <t>26934</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16505</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>40103</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20640</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41896</t>
+          <t>41295</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>24331</t>
+          <t>25586</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>35459</t>
+          <t>34606</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>59976</t>
+          <t>59525</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>53301</t>
+          <t>52014</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>77881</t>
+          <t>77484</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>105291</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>58035</t>
+          <t>59819</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>88848</t>
+          <t>89144</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>34862</t>
+          <t>35022</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>58622</t>
+          <t>58863</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>99410</t>
+          <t>101732</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>139313</t>
+          <t>138970</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>48045</t>
+          <t>45596</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>76325</t>
+          <t>74703</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>39180</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>64165</t>
+          <t>62441</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>128805</t>
+          <t>132732</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>109722</t>
+          <t>110609</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>143730</t>
+          <t>146822</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>58434</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>85529</t>
+          <t>84763</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>176458</t>
+          <t>176299</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>221428</t>
+          <t>221107</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>18206</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>24138</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>25298</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>18813</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>42265</t>
+          <t>42761</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t>40084</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>68365</t>
+          <t>69990</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>65114</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>85791</t>
+          <t>82531</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>123495</t>
+          <t>122132</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>115155</t>
+          <t>112204</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>154227</t>
+          <t>151366</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>70869</t>
+          <t>72141</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>100196</t>
+          <t>103957</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>193134</t>
+          <t>192303</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>243293</t>
+          <t>242869</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>134552</t>
+          <t>133805</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>173934</t>
+          <t>173686</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>90815</t>
+          <t>90580</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>124496</t>
+          <t>123685</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>237880</t>
+          <t>235787</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>287314</t>
+          <t>288007</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>53200</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>52659</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>86170</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>76411</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>58554</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>126259</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>228258</t>
+          <t>228725</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>288581</t>
+          <t>290790</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>177522</t>
+          <t>179181</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>231237</t>
+          <t>232405</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>422586</t>
+          <t>424898</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>496707</t>
+          <t>506140</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>320767</t>
+          <t>321746</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>384439</t>
+          <t>386097</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>198333</t>
+          <t>196910</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>249894</t>
+          <t>250654</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>535456</t>
+          <t>534020</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>617638</t>
+          <t>617194</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>675599</t>
+          <t>672895</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>751415</t>
+          <t>751637</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>412159</t>
+          <t>413914</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>476624</t>
+          <t>477932</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1112674</t>
+          <t>1107715</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1208325</t>
+          <t>1209447</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21916</t>
+          <t>21129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24101</t>
+          <t>23982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32749</t>
+          <t>32831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24093</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>45263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19430</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77180</t>
+          <t>75189</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34841</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27656</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>31694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54702</t>
+          <t>55763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68852</t>
+          <t>68596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53838</t>
+          <t>54028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>85129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116001</t>
+          <t>115949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19410</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25818</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46875</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28677</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43530</t>
+          <t>42905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>69783</t>
+          <t>68749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29793</t>
+          <t>29206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>52613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10850</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27700</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45058</t>
+          <t>45420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72579</t>
+          <t>72559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70494</t>
+          <t>69513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95980</t>
+          <t>96733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54886</t>
+          <t>54281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76304</t>
+          <t>76197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132698</t>
+          <t>132178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165135</t>
+          <t>165626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -8469,62 +8469,62 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9961</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9251</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1898</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6015</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16859</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>35631</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33737</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56122</t>
+          <t>57722</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42272</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63698</t>
+          <t>62590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>20773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>37260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66211</t>
+          <t>65612</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>94283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34582</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55986</t>
+          <t>56905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43895</t>
+          <t>42652</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66408</t>
+          <t>65479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93715</t>
+          <t>93189</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>22803</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>22071</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>22571</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>35686</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60595</t>
+          <t>61609</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82250</t>
+          <t>82921</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57596</t>
+          <t>56484</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>104162</t>
+          <t>104441</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133178</t>
+          <t>133430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>32659</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46126</t>
+          <t>45803</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21045</t>
+          <t>21660</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>35330</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54863</t>
+          <t>54093</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77757</t>
+          <t>77815</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,07%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40006</t>
+          <t>39481</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>22509</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>36382</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56993</t>
+          <t>58020</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13994</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31842</t>
+          <t>33001</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15572</t>
+          <t>16135</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>33969</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>21631</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>50654</t>
+          <t>49232</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29233</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>50090</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>37383</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>56482</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>82484</t>
+          <t>82017</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>23822</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>44376</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28998</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>42003</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>65822</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>32254</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>16537</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>37800</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33547</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>61215</t>
+          <t>62827</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>29757</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>54707</t>
+          <t>55648</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>22867</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>44583</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>59600</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>92300</t>
+          <t>92799</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>106636</t>
+          <t>105763</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>144232</t>
+          <t>145143</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>80730</t>
+          <t>79499</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>113160</t>
+          <t>111858</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>195561</t>
+          <t>195980</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>247372</t>
+          <t>245475</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>53674</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>84503</t>
+          <t>85596</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>47458</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>74299</t>
+          <t>73819</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>107757</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>150760</t>
+          <t>150018</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>86129</t>
+          <t>85821</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>122964</t>
+          <t>123948</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>57147</t>
+          <t>58186</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>86618</t>
+          <t>86323</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>152532</t>
+          <t>152372</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>199093</t>
+          <t>200408</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17705</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>22301</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>63293</t>
+          <t>62628</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>32109</t>
+          <t>31754</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>56565</t>
+          <t>55225</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>75990</t>
+          <t>74941</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>111491</t>
+          <t>113642</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>102080</t>
+          <t>102287</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>137113</t>
+          <t>137183</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>65007</t>
+          <t>65364</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>95491</t>
+          <t>94654</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>177715</t>
+          <t>176972</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>224582</t>
+          <t>220503</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>135860</t>
+          <t>135481</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>174078</t>
+          <t>171993</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>92021</t>
+          <t>93597</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>123453</t>
+          <t>123978</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>236971</t>
+          <t>239270</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>285131</t>
+          <t>286127</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>68722</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>63619</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>76274</t>
+          <t>78002</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>119216</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>65926</t>
+          <t>65818</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>102946</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>82653</t>
+          <t>82095</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>126851</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>178353</t>
+          <t>172993</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>285020</t>
+          <t>283049</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>346451</t>
+          <t>351058</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>217748</t>
+          <t>214512</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>273258</t>
+          <t>271533</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>518717</t>
+          <t>522129</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>604195</t>
+          <t>606742</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>361422</t>
+          <t>359859</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>429420</t>
+          <t>427779</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>246588</t>
+          <t>242759</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>301393</t>
+          <t>301066</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>619278</t>
+          <t>623402</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>709876</t>
+          <t>709259</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>542482</t>
+          <t>541249</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>615831</t>
+          <t>618291</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>373985</t>
+          <t>374366</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>436224</t>
+          <t>439866</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,47 +13063,47 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
+          <t>42,41%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>985952</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>933471</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>1034456</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>40,09%</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>37,95%</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
           <t>42,06%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>985952</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>930975</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>1034850</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>40,09%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>37,85%</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>42,08%</t>
         </is>
       </c>
     </row>
